--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/105.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/105.xlsx
@@ -426,13 +426,13 @@
         <v>-22.93493897546757</v>
       </c>
       <c r="E2">
-        <v>-26.24941546830298</v>
+        <v>-21.87083013093262</v>
       </c>
       <c r="F2">
-        <v>-5.578117721569612</v>
+        <v>-4.446851150997245</v>
       </c>
       <c r="G2">
-        <v>-16.78273245471137</v>
+        <v>-12.64272986025822</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.62159535456132</v>
       </c>
       <c r="E3">
-        <v>-27.44495888026813</v>
+        <v>-22.19976031464772</v>
       </c>
       <c r="F3">
-        <v>-5.689421307646767</v>
+        <v>-4.424377543359294</v>
       </c>
       <c r="G3">
-        <v>-15.62328642270271</v>
+        <v>-12.52505707467527</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.3472957954582</v>
       </c>
       <c r="E4">
-        <v>-27.9549109327872</v>
+        <v>-22.01915376697622</v>
       </c>
       <c r="F4">
-        <v>-5.75890476539359</v>
+        <v>-4.287353977792616</v>
       </c>
       <c r="G4">
-        <v>-14.84505087291004</v>
+        <v>-12.23942464656763</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.14137812913183</v>
       </c>
       <c r="E5">
-        <v>-28.24314795194163</v>
+        <v>-22.78350662598634</v>
       </c>
       <c r="F5">
-        <v>-5.247431797637244</v>
+        <v>-4.382500257678168</v>
       </c>
       <c r="G5">
-        <v>-15.05557217913135</v>
+        <v>-12.13895144635094</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.00467985423257</v>
       </c>
       <c r="E6">
-        <v>-31.33450773735126</v>
+        <v>-22.94681920170125</v>
       </c>
       <c r="F6">
-        <v>-5.429998174642435</v>
+        <v>-4.663618332961819</v>
       </c>
       <c r="G6">
-        <v>-14.85929117928227</v>
+        <v>-11.98393979162588</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.92646544387598</v>
       </c>
       <c r="E7">
-        <v>-28.66054776669256</v>
+        <v>-23.79588095889257</v>
       </c>
       <c r="F7">
-        <v>-4.970578986110607</v>
+        <v>-4.306281344579182</v>
       </c>
       <c r="G7">
-        <v>-14.90664747542047</v>
+        <v>-11.74552006870394</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.90227650851994</v>
       </c>
       <c r="E8">
-        <v>-29.37751871430337</v>
+        <v>-24.01788671704996</v>
       </c>
       <c r="F8">
-        <v>-5.374066807605413</v>
+        <v>-3.937820210344351</v>
       </c>
       <c r="G8">
-        <v>-14.8913341530213</v>
+        <v>-11.49286134478206</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.91189085445354</v>
       </c>
       <c r="E9">
-        <v>-29.17365833642416</v>
+        <v>-24.76648644550501</v>
       </c>
       <c r="F9">
-        <v>-4.652361648325177</v>
+        <v>-4.181042133684731</v>
       </c>
       <c r="G9">
-        <v>-14.92675281951664</v>
+        <v>-10.57714137407678</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.94623068338309</v>
       </c>
       <c r="E10">
-        <v>-29.8500524093914</v>
+        <v>-26.06540328734513</v>
       </c>
       <c r="F10">
-        <v>-5.336787789377226</v>
+        <v>-3.741110288303761</v>
       </c>
       <c r="G10">
-        <v>-14.03879811753785</v>
+        <v>-10.968802666891</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.98819360669627</v>
       </c>
       <c r="E11">
-        <v>-30.32221854527718</v>
+        <v>-26.27146071401517</v>
       </c>
       <c r="F11">
-        <v>-4.815971665684704</v>
+        <v>-3.740536229693621</v>
       </c>
       <c r="G11">
-        <v>-13.69786881361814</v>
+        <v>-10.30436947382497</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-22.03368681088915</v>
       </c>
       <c r="E12">
-        <v>-30.68518637240491</v>
+        <v>-27.09592300052954</v>
       </c>
       <c r="F12">
-        <v>-5.266783288534043</v>
+        <v>-3.449488514352612</v>
       </c>
       <c r="G12">
-        <v>-14.52958416098746</v>
+        <v>-9.792044787498671</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-22.07217786976964</v>
       </c>
       <c r="E13">
-        <v>-30.81637178191661</v>
+        <v>-27.25491623646662</v>
       </c>
       <c r="F13">
-        <v>-4.985658586311169</v>
+        <v>-3.522840447870508</v>
       </c>
       <c r="G13">
-        <v>-13.15809345328858</v>
+        <v>-10.10687447774102</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-22.09622058466332</v>
       </c>
       <c r="E14">
-        <v>-32.55666077427458</v>
+        <v>-29.36000669875223</v>
       </c>
       <c r="F14">
-        <v>-4.502722875581266</v>
+        <v>-3.164294043079784</v>
       </c>
       <c r="G14">
-        <v>-13.66649288512214</v>
+        <v>-9.603411963929259</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-22.091284519304</v>
       </c>
       <c r="E15">
-        <v>-34.83682778335267</v>
+        <v>-28.92264655037417</v>
       </c>
       <c r="F15">
-        <v>-4.080743408553767</v>
+        <v>-3.290116424625806</v>
       </c>
       <c r="G15">
-        <v>-13.38943283687942</v>
+        <v>-10.01617198915656</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-22.03645600096278</v>
       </c>
       <c r="E16">
-        <v>-33.78186849812731</v>
+        <v>-29.63621601790995</v>
       </c>
       <c r="F16">
-        <v>-4.0603067563593</v>
+        <v>-2.884597446259336</v>
       </c>
       <c r="G16">
-        <v>-12.92860117149595</v>
+        <v>-9.016178488422444</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-21.91587295181869</v>
       </c>
       <c r="E17">
-        <v>-35.13817649065957</v>
+        <v>-31.07318560418738</v>
       </c>
       <c r="F17">
-        <v>-4.134527647282733</v>
+        <v>-2.921048097084723</v>
       </c>
       <c r="G17">
-        <v>-13.77820273005899</v>
+        <v>-9.270171302830377</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-21.71273733103508</v>
       </c>
       <c r="E18">
-        <v>-34.80745004304649</v>
+        <v>-31.31106701263392</v>
       </c>
       <c r="F18">
-        <v>-4.198445304450146</v>
+        <v>-2.724679462414086</v>
       </c>
       <c r="G18">
-        <v>-13.10933257656036</v>
+        <v>-9.796583566970321</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-21.42896494742857</v>
       </c>
       <c r="E19">
-        <v>-35.69529448758907</v>
+        <v>-31.99015028993399</v>
       </c>
       <c r="F19">
-        <v>-4.482245633384061</v>
+        <v>-2.327236237857509</v>
       </c>
       <c r="G19">
-        <v>-12.58131731524147</v>
+        <v>-9.044195694001976</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-21.06413880398978</v>
       </c>
       <c r="E20">
-        <v>-36.13820747950842</v>
+        <v>-32.52905230199278</v>
       </c>
       <c r="F20">
-        <v>-3.67888581410767</v>
+        <v>-2.127034747214119</v>
       </c>
       <c r="G20">
-        <v>-12.44064909129999</v>
+        <v>-9.137486735848523</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-20.63733395112781</v>
       </c>
       <c r="E21">
-        <v>-36.26659570119284</v>
+        <v>-33.03765248422562</v>
       </c>
       <c r="F21">
-        <v>-3.145730329583047</v>
+        <v>-1.952520929731541</v>
       </c>
       <c r="G21">
-        <v>-11.52156648156135</v>
+        <v>-9.294619620553858</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-20.15625103795416</v>
       </c>
       <c r="E22">
-        <v>-35.77403729770215</v>
+        <v>-33.43624448149206</v>
       </c>
       <c r="F22">
-        <v>-3.228342582296839</v>
+        <v>-1.61307253541236</v>
       </c>
       <c r="G22">
-        <v>-12.89855411199682</v>
+        <v>-9.470038160375349</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.64661100001224</v>
       </c>
       <c r="E23">
-        <v>-38.58600640407924</v>
+        <v>-33.99363451376333</v>
       </c>
       <c r="F23">
-        <v>-3.542616891244943</v>
+        <v>-1.505342526310881</v>
       </c>
       <c r="G23">
-        <v>-12.87459008739499</v>
+        <v>-9.541487712972643</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.11892337399897</v>
       </c>
       <c r="E24">
-        <v>-37.83190782383012</v>
+        <v>-33.53848408467537</v>
       </c>
       <c r="F24">
-        <v>-2.575134295186692</v>
+        <v>-1.704346197689823</v>
       </c>
       <c r="G24">
-        <v>-12.07731176655475</v>
+        <v>-9.811835536871605</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-18.60379854774679</v>
       </c>
       <c r="E25">
-        <v>-37.90482367845447</v>
+        <v>-33.35953674492814</v>
       </c>
       <c r="F25">
-        <v>-3.263647601004154</v>
+        <v>-1.539450554121151</v>
       </c>
       <c r="G25">
-        <v>-12.7378640877861</v>
+        <v>-10.02895811079154</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.11341052661196</v>
       </c>
       <c r="E26">
-        <v>-38.04462284825387</v>
+        <v>-34.73492043707535</v>
       </c>
       <c r="F26">
-        <v>-3.380668578895432</v>
+        <v>-1.420685034479577</v>
       </c>
       <c r="G26">
-        <v>-13.07721389122818</v>
+        <v>-9.641340861348953</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-17.67750513930771</v>
       </c>
       <c r="E27">
-        <v>-37.38603566884183</v>
+        <v>-34.24304108363627</v>
       </c>
       <c r="F27">
-        <v>-3.298314776811313</v>
+        <v>-1.323720488144881</v>
       </c>
       <c r="G27">
-        <v>-12.90943308470799</v>
+        <v>-9.720037840931177</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-17.30612588172037</v>
       </c>
       <c r="E28">
-        <v>-37.90271800031278</v>
+        <v>-33.45539078569952</v>
       </c>
       <c r="F28">
-        <v>-3.42518007291746</v>
+        <v>-1.552939688908338</v>
       </c>
       <c r="G28">
-        <v>-12.27323378902255</v>
+        <v>-9.91009482567504</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.02407455251926</v>
       </c>
       <c r="E29">
-        <v>-37.89528167543568</v>
+        <v>-33.43038222370707</v>
       </c>
       <c r="F29">
-        <v>-2.940441006351663</v>
+        <v>-1.499186928140678</v>
       </c>
       <c r="G29">
-        <v>-12.74099698129543</v>
+        <v>-10.66490416425165</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-16.83686590509411</v>
       </c>
       <c r="E30">
-        <v>-36.53714626992048</v>
+        <v>-34.15523596641241</v>
       </c>
       <c r="F30">
-        <v>-3.318164944884598</v>
+        <v>-1.365499198105074</v>
       </c>
       <c r="G30">
-        <v>-13.06721343407192</v>
+        <v>-10.23690261210142</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.75633782992227</v>
       </c>
       <c r="E31">
-        <v>-36.66716670365557</v>
+        <v>-33.6759387666819</v>
       </c>
       <c r="F31">
-        <v>-3.268939211973237</v>
+        <v>-1.511389608351318</v>
       </c>
       <c r="G31">
-        <v>-12.54153478916208</v>
+        <v>-10.7094264971362</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.77723294145428</v>
       </c>
       <c r="E32">
-        <v>-35.85702053657788</v>
+        <v>-32.43833993684154</v>
       </c>
       <c r="F32">
-        <v>-2.921110224639933</v>
+        <v>-1.27974080599545</v>
       </c>
       <c r="G32">
-        <v>-13.91516369668109</v>
+        <v>-10.57860991790928</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-16.892955179286</v>
       </c>
       <c r="E33">
-        <v>-36.25116652112111</v>
+        <v>-32.24979452572263</v>
       </c>
       <c r="F33">
-        <v>-2.335553046581616</v>
+        <v>-1.246871187452366</v>
       </c>
       <c r="G33">
-        <v>-12.491674788961</v>
+        <v>-10.53406278295112</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-17.08965133028888</v>
       </c>
       <c r="E34">
-        <v>-35.96230859687362</v>
+        <v>-32.47713716043242</v>
       </c>
       <c r="F34">
-        <v>-2.32811844914149</v>
+        <v>-1.239186423056595</v>
       </c>
       <c r="G34">
-        <v>-13.03696926335617</v>
+        <v>-10.23979662248067</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.34678489322372</v>
       </c>
       <c r="E35">
-        <v>-36.47406314310766</v>
+        <v>-31.25120470120351</v>
       </c>
       <c r="F35">
-        <v>-3.137208085743046</v>
+        <v>-1.111594648738192</v>
       </c>
       <c r="G35">
-        <v>-14.18230683159446</v>
+        <v>-10.82731727989251</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.64887435998971</v>
       </c>
       <c r="E36">
-        <v>-34.66845867284978</v>
+        <v>-31.5998647153172</v>
       </c>
       <c r="F36">
-        <v>-3.146596801886375</v>
+        <v>-1.168502660943116</v>
       </c>
       <c r="G36">
-        <v>-12.71896490769103</v>
+        <v>-10.86176083328306</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.97167998334005</v>
       </c>
       <c r="E37">
-        <v>-36.31454037272666</v>
+        <v>-30.29640010707639</v>
       </c>
       <c r="F37">
-        <v>-2.990220917055496</v>
+        <v>-0.8283725202514302</v>
       </c>
       <c r="G37">
-        <v>-14.10471811309116</v>
+        <v>-11.47019224949742</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-18.30714404856724</v>
       </c>
       <c r="E38">
-        <v>-33.58799451687864</v>
+        <v>-29.70915679180225</v>
       </c>
       <c r="F38">
-        <v>-2.664612885302289</v>
+        <v>-0.9880511059172713</v>
       </c>
       <c r="G38">
-        <v>-14.68875995333534</v>
+        <v>-11.17238200324454</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-18.63652781140744</v>
       </c>
       <c r="E39">
-        <v>-33.2604265864781</v>
+        <v>-29.29296971475817</v>
       </c>
       <c r="F39">
-        <v>-2.388401230145419</v>
+        <v>-1.137304687818881</v>
       </c>
       <c r="G39">
-        <v>-13.40818059378821</v>
+        <v>-11.4799538235236</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-18.96170683260164</v>
       </c>
       <c r="E40">
-        <v>-32.26899066846599</v>
+        <v>-29.42648715242876</v>
       </c>
       <c r="F40">
-        <v>-3.053238967223468</v>
+        <v>-0.8627588795090404</v>
       </c>
       <c r="G40">
-        <v>-13.20358306704414</v>
+        <v>-11.53212041657093</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-19.27014169563035</v>
       </c>
       <c r="E41">
-        <v>-33.72594758424415</v>
+        <v>-28.14298495442074</v>
       </c>
       <c r="F41">
-        <v>-3.259765871354635</v>
+        <v>-1.227759094734975</v>
       </c>
       <c r="G41">
-        <v>-14.90885616534456</v>
+        <v>-11.71818426746269</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-19.57011990294681</v>
       </c>
       <c r="E42">
-        <v>-32.17818070284861</v>
+        <v>-27.29429698624865</v>
       </c>
       <c r="F42">
-        <v>-2.623836499899483</v>
+        <v>-1.001644614997211</v>
       </c>
       <c r="G42">
-        <v>-13.33810820896272</v>
+        <v>-11.62680951214602</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-19.85362385918872</v>
       </c>
       <c r="E43">
-        <v>-32.26765956423638</v>
+        <v>-27.03929811732683</v>
       </c>
       <c r="F43">
-        <v>-2.97572614424131</v>
+        <v>-1.053392726650096</v>
       </c>
       <c r="G43">
-        <v>-15.13191818320927</v>
+        <v>-11.87027580436258</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-20.13173958533532</v>
       </c>
       <c r="E44">
-        <v>-31.44999193144944</v>
+        <v>-27.10396777086573</v>
       </c>
       <c r="F44">
-        <v>-1.981392847188715</v>
+        <v>-1.194915983948781</v>
       </c>
       <c r="G44">
-        <v>-14.25392869333476</v>
+        <v>-11.91402927296505</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-20.3989749911726</v>
       </c>
       <c r="E45">
-        <v>-31.07879036287024</v>
+        <v>-26.97841203930484</v>
       </c>
       <c r="F45">
-        <v>-3.830291494521753</v>
+        <v>-1.302686583052996</v>
       </c>
       <c r="G45">
-        <v>-14.12255602550994</v>
+        <v>-12.21811574921497</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-20.66558624301328</v>
       </c>
       <c r="E46">
-        <v>-31.12347891672539</v>
+        <v>-25.8765276959259</v>
       </c>
       <c r="F46">
-        <v>-2.509883794868175</v>
+        <v>-1.020033542971957</v>
       </c>
       <c r="G46">
-        <v>-14.36145482006436</v>
+        <v>-11.8415680568387</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-20.926061644605</v>
       </c>
       <c r="E47">
-        <v>-31.09849112078956</v>
+        <v>-26.93543045530419</v>
       </c>
       <c r="F47">
-        <v>-3.079441884908822</v>
+        <v>-1.04260241286123</v>
       </c>
       <c r="G47">
-        <v>-15.27411630348115</v>
+        <v>-11.63129346598125</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-21.186088025122</v>
       </c>
       <c r="E48">
-        <v>-30.15756240569869</v>
+        <v>-24.50394534481729</v>
       </c>
       <c r="F48">
-        <v>-2.778201108676365</v>
+        <v>-0.9759685389800377</v>
       </c>
       <c r="G48">
-        <v>-13.40452163524376</v>
+        <v>-12.65449387538578</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-21.43969065387105</v>
       </c>
       <c r="E49">
-        <v>-28.18567789023431</v>
+        <v>-24.22960081754442</v>
       </c>
       <c r="F49">
-        <v>-2.945393815053001</v>
+        <v>-1.35332468238613</v>
       </c>
       <c r="G49">
-        <v>-14.65973891646053</v>
+        <v>-11.47782737205414</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-21.68889081754149</v>
       </c>
       <c r="E50">
-        <v>-29.86928800764234</v>
+        <v>-24.49607500935674</v>
       </c>
       <c r="F50">
-        <v>-3.344794471782393</v>
+        <v>-1.260487062452181</v>
       </c>
       <c r="G50">
-        <v>-14.21735868847474</v>
+        <v>-11.52737799902117</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-21.92844888318421</v>
       </c>
       <c r="E51">
-        <v>-28.70722778537797</v>
+        <v>-23.24189655990767</v>
       </c>
       <c r="F51">
-        <v>-3.376023094500532</v>
+        <v>-1.299348262419714</v>
       </c>
       <c r="G51">
-        <v>-14.81757409146087</v>
+        <v>-11.82009859869368</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-22.15526983021798</v>
       </c>
       <c r="E52">
-        <v>-29.27024749560004</v>
+        <v>-23.73641527914368</v>
       </c>
       <c r="F52">
-        <v>-3.259924917895973</v>
+        <v>-1.24539006653616</v>
       </c>
       <c r="G52">
-        <v>-14.23656724180386</v>
+        <v>-11.64333683078006</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-22.36522838526268</v>
       </c>
       <c r="E53">
-        <v>-28.27183210595656</v>
+        <v>-22.77453153631339</v>
       </c>
       <c r="F53">
-        <v>-3.491012087152743</v>
+        <v>-1.518966684984725</v>
       </c>
       <c r="G53">
-        <v>-14.19683431987171</v>
+        <v>-12.33371951970946</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-22.55080849178308</v>
       </c>
       <c r="E54">
-        <v>-28.78452735455568</v>
+        <v>-22.34298380718443</v>
       </c>
       <c r="F54">
-        <v>-3.866540852068259</v>
+        <v>-1.395385865630678</v>
       </c>
       <c r="G54">
-        <v>-13.25568308610439</v>
+        <v>-11.67757413534792</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-22.71173356166618</v>
       </c>
       <c r="E55">
-        <v>-27.58920821600207</v>
+        <v>-22.14796561621578</v>
       </c>
       <c r="F55">
-        <v>-2.595281847157581</v>
+        <v>-1.522913027291662</v>
       </c>
       <c r="G55">
-        <v>-13.91617013872096</v>
+        <v>-12.26334689925601</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-22.83845845903258</v>
       </c>
       <c r="E56">
-        <v>-24.72154454575903</v>
+        <v>-20.88645674877839</v>
       </c>
       <c r="F56">
-        <v>-3.395740723789369</v>
+        <v>-1.176372151269711</v>
       </c>
       <c r="G56">
-        <v>-15.13398197680855</v>
+        <v>-11.99356430156102</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-22.93490349495625</v>
       </c>
       <c r="E57">
-        <v>-26.77537399726794</v>
+        <v>-20.88091636487106</v>
       </c>
       <c r="F57">
-        <v>-3.386598032764671</v>
+        <v>-1.504829766888548</v>
       </c>
       <c r="G57">
-        <v>-13.9930108788989</v>
+        <v>-11.34615185785675</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-22.99358684605872</v>
       </c>
       <c r="E58">
-        <v>-26.50266168204573</v>
+        <v>-21.76421304301295</v>
       </c>
       <c r="F58">
-        <v>-3.162088100686129</v>
+        <v>-1.580974126921282</v>
       </c>
       <c r="G58">
-        <v>-14.00414309383541</v>
+        <v>-12.01197396704525</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-23.02504975766352</v>
       </c>
       <c r="E59">
-        <v>-25.61873786899379</v>
+        <v>-20.6680642844736</v>
       </c>
       <c r="F59">
-        <v>-2.908925768512155</v>
+        <v>-1.45847184192568</v>
       </c>
       <c r="G59">
-        <v>-14.72278970370821</v>
+        <v>-12.08278780333461</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-23.02483124558932</v>
       </c>
       <c r="E60">
-        <v>-23.93806199538675</v>
+        <v>-19.24230836877321</v>
       </c>
       <c r="F60">
-        <v>-3.291300161644407</v>
+        <v>-1.381333441009587</v>
       </c>
       <c r="G60">
-        <v>-14.58690566922994</v>
+        <v>-11.93661612979506</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-23.00749601239472</v>
       </c>
       <c r="E61">
-        <v>-25.80362222432986</v>
+        <v>-20.1988718478964</v>
       </c>
       <c r="F61">
-        <v>-3.231122583300634</v>
+        <v>-1.329989572649268</v>
       </c>
       <c r="G61">
-        <v>-15.58070648379394</v>
+        <v>-11.75190203385691</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-22.96862853400269</v>
       </c>
       <c r="E62">
-        <v>-25.25166459247147</v>
+        <v>-19.0064807233268</v>
       </c>
       <c r="F62">
-        <v>-3.356742843200374</v>
+        <v>-1.633945737228102</v>
       </c>
       <c r="G62">
-        <v>-13.92528946957772</v>
+        <v>-11.74941791037847</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-22.92322193040795</v>
       </c>
       <c r="E63">
-        <v>-26.04175905527288</v>
+        <v>-19.21665398241974</v>
       </c>
       <c r="F63">
-        <v>-3.569852783081588</v>
+        <v>-1.349333608239442</v>
       </c>
       <c r="G63">
-        <v>-13.92828399362373</v>
+        <v>-12.30058394935905</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-22.86586228488981</v>
       </c>
       <c r="E64">
-        <v>-28.00816756160548</v>
+        <v>-19.47139535223943</v>
       </c>
       <c r="F64">
-        <v>-3.554377223262488</v>
+        <v>-1.793684793714347</v>
       </c>
       <c r="G64">
-        <v>-14.67336961397073</v>
+        <v>-12.41222199881965</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-22.81012628614737</v>
       </c>
       <c r="E65">
-        <v>-25.66693588641843</v>
+        <v>-19.26382615664715</v>
       </c>
       <c r="F65">
-        <v>-3.033638137738426</v>
+        <v>-1.863522792709568</v>
       </c>
       <c r="G65">
-        <v>-15.70027728069464</v>
+        <v>-12.25837343080993</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-22.74791075465496</v>
       </c>
       <c r="E66">
-        <v>-24.41968499345917</v>
+        <v>-18.50164958037124</v>
       </c>
       <c r="F66">
-        <v>-3.589822236060876</v>
+        <v>-1.980786482249866</v>
       </c>
       <c r="G66">
-        <v>-15.43790789226612</v>
+        <v>-12.35306513712961</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-22.68839013413993</v>
       </c>
       <c r="E67">
-        <v>-23.26878445002461</v>
+        <v>-18.94647512610567</v>
       </c>
       <c r="F67">
-        <v>-3.209201496720351</v>
+        <v>-2.003535107865546</v>
       </c>
       <c r="G67">
-        <v>-14.78602585382186</v>
+        <v>-12.0265601970758</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-22.62092980104127</v>
       </c>
       <c r="E68">
-        <v>-25.27697426228498</v>
+        <v>-18.64147574604424</v>
       </c>
       <c r="F68">
-        <v>-3.881333837147453</v>
+        <v>-1.895168084231315</v>
       </c>
       <c r="G68">
-        <v>-15.03240182088522</v>
+        <v>-12.00237686992832</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-22.55136116355739</v>
       </c>
       <c r="E69">
-        <v>-25.16236224256501</v>
+        <v>-18.07844980600518</v>
       </c>
       <c r="F69">
-        <v>-4.33849489613925</v>
+        <v>-1.969717837013659</v>
       </c>
       <c r="G69">
-        <v>-15.45162082823094</v>
+        <v>-12.16109056048358</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.46992538088558</v>
       </c>
       <c r="E70">
-        <v>-24.20596904510614</v>
+        <v>-18.49875894528916</v>
       </c>
       <c r="F70">
-        <v>-3.813213872145639</v>
+        <v>-1.99056701617472</v>
       </c>
       <c r="G70">
-        <v>-14.39090401905211</v>
+        <v>-12.09578800602606</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.38179294838403</v>
       </c>
       <c r="E71">
-        <v>-22.87491465403449</v>
+        <v>-18.95336115048224</v>
       </c>
       <c r="F71">
-        <v>-3.805842230628126</v>
+        <v>-2.198413509578546</v>
       </c>
       <c r="G71">
-        <v>-15.30903762313188</v>
+        <v>-11.83013299552962</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-22.28236102134775</v>
       </c>
       <c r="E72">
-        <v>-24.1621858913198</v>
+        <v>-18.58256244340155</v>
       </c>
       <c r="F72">
-        <v>-3.671699726888385</v>
+        <v>-2.113118174847087</v>
       </c>
       <c r="G72">
-        <v>-14.49783097989804</v>
+        <v>-11.66102593075715</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-22.17691356633438</v>
       </c>
       <c r="E73">
-        <v>-25.24499868829512</v>
+        <v>-18.05762560442249</v>
       </c>
       <c r="F73">
-        <v>-3.623545901396247</v>
+        <v>-2.157273470885912</v>
       </c>
       <c r="G73">
-        <v>-14.30451448053218</v>
+        <v>-12.29154555158462</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-22.0653993224938</v>
       </c>
       <c r="E74">
-        <v>-25.22069409562223</v>
+        <v>-19.00673822242894</v>
       </c>
       <c r="F74">
-        <v>-3.768057079916829</v>
+        <v>-2.374397679201093</v>
       </c>
       <c r="G74">
-        <v>-13.75181593447661</v>
+        <v>-11.24683260674932</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-21.95020917525984</v>
       </c>
       <c r="E75">
-        <v>-25.79450177226054</v>
+        <v>-18.78521423678523</v>
       </c>
       <c r="F75">
-        <v>-4.049890036269097</v>
+        <v>-2.313515988564941</v>
       </c>
       <c r="G75">
-        <v>-14.45860976390575</v>
+        <v>-11.36218574576307</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-21.83358177550704</v>
       </c>
       <c r="E76">
-        <v>-24.62414343376916</v>
+        <v>-18.4310366814265</v>
       </c>
       <c r="F76">
-        <v>-4.111918187390724</v>
+        <v>-2.265607359824031</v>
       </c>
       <c r="G76">
-        <v>-14.8254689831044</v>
+        <v>-11.16196774307059</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-21.71174305233985</v>
       </c>
       <c r="E77">
-        <v>-25.51556794647373</v>
+        <v>-19.16613847307585</v>
       </c>
       <c r="F77">
-        <v>-3.982968718899133</v>
+        <v>-2.988204670797082</v>
       </c>
       <c r="G77">
-        <v>-14.90920600511977</v>
+        <v>-11.249746197713</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-21.5857533750102</v>
       </c>
       <c r="E78">
-        <v>-25.30138683845232</v>
+        <v>-18.39888667256101</v>
       </c>
       <c r="F78">
-        <v>-4.656465380438646</v>
+        <v>-2.051800762957062</v>
       </c>
       <c r="G78">
-        <v>-13.462796065262</v>
+        <v>-11.32216564192589</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-21.44590509204113</v>
       </c>
       <c r="E79">
-        <v>-26.23747083253278</v>
+        <v>-18.57744568704936</v>
       </c>
       <c r="F79">
-        <v>-4.639776262374443</v>
+        <v>-2.646469982446174</v>
       </c>
       <c r="G79">
-        <v>-14.41238522554779</v>
+        <v>-11.05059729493058</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-21.29388603231592</v>
       </c>
       <c r="E80">
-        <v>-24.3324052574679</v>
+        <v>-19.14128565650808</v>
       </c>
       <c r="F80">
-        <v>-3.737622033170572</v>
+        <v>-2.522527166537103</v>
       </c>
       <c r="G80">
-        <v>-14.53700781323229</v>
+        <v>-10.72390307589392</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-21.11802015482455</v>
       </c>
       <c r="E81">
-        <v>-26.77166102634355</v>
+        <v>-19.57681631529755</v>
       </c>
       <c r="F81">
-        <v>-4.419670759776587</v>
+        <v>-2.893291162151717</v>
       </c>
       <c r="G81">
-        <v>-13.92598914912814</v>
+        <v>-10.20530215957058</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-20.92298526691944</v>
       </c>
       <c r="E82">
-        <v>-26.57141809552827</v>
+        <v>-20.91189516814296</v>
       </c>
       <c r="F82">
-        <v>-4.5754054882377</v>
+        <v>-2.593762621340847</v>
       </c>
       <c r="G82">
-        <v>-13.67113609437743</v>
+        <v>-10.19973996821922</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-20.69770045862287</v>
       </c>
       <c r="E83">
-        <v>-27.07405634290431</v>
+        <v>-21.80521769842298</v>
       </c>
       <c r="F83">
-        <v>-4.248754541924368</v>
+        <v>-2.871752781311527</v>
       </c>
       <c r="G83">
-        <v>-13.68796756475634</v>
+        <v>-10.33119617987095</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-20.45038186073167</v>
       </c>
       <c r="E84">
-        <v>-27.95670927329085</v>
+        <v>-21.31711569068383</v>
       </c>
       <c r="F84">
-        <v>-4.24806865371485</v>
+        <v>-3.021287179762686</v>
       </c>
       <c r="G84">
-        <v>-14.43824073460588</v>
+        <v>-10.40203090211704</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-20.17400465908739</v>
       </c>
       <c r="E85">
-        <v>-28.88508906036375</v>
+        <v>-22.45980118211788</v>
       </c>
       <c r="F85">
-        <v>-4.376338860936145</v>
+        <v>-3.008079689892451</v>
       </c>
       <c r="G85">
-        <v>-13.05748318898084</v>
+        <v>-10.48006866869001</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-19.88373494969939</v>
       </c>
       <c r="E86">
-        <v>-28.40182762042369</v>
+        <v>-22.31882042369658</v>
       </c>
       <c r="F86">
-        <v>-4.930598661781891</v>
+        <v>-3.092887944591064</v>
       </c>
       <c r="G86">
-        <v>-13.51642336990806</v>
+        <v>-10.40817267876763</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-19.57919002950698</v>
       </c>
       <c r="E87">
-        <v>-29.96979779830886</v>
+        <v>-24.94024434770186</v>
       </c>
       <c r="F87">
-        <v>-4.426880041283152</v>
+        <v>-3.176034494279661</v>
       </c>
       <c r="G87">
-        <v>-13.18378056932054</v>
+        <v>-9.635246078100998</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-19.28070072017273</v>
       </c>
       <c r="E88">
-        <v>-30.15741704330232</v>
+        <v>-24.00462136007846</v>
       </c>
       <c r="F88">
-        <v>-5.119674349838282</v>
+        <v>-3.006902579813072</v>
       </c>
       <c r="G88">
-        <v>-13.83454912519669</v>
+        <v>-9.587828429464905</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-18.99357574407061</v>
       </c>
       <c r="E89">
-        <v>-31.04658428565185</v>
+        <v>-27.25454244744739</v>
       </c>
       <c r="F89">
-        <v>-4.632837857008595</v>
+        <v>-3.419803140105889</v>
       </c>
       <c r="G89">
-        <v>-12.63685307418363</v>
+        <v>-9.754016681784515</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.73956180290981</v>
       </c>
       <c r="E90">
-        <v>-33.27956043105158</v>
+        <v>-26.68274492509029</v>
       </c>
       <c r="F90">
-        <v>-4.866581600526143</v>
+        <v>-3.316026928617972</v>
       </c>
       <c r="G90">
-        <v>-13.27653118703673</v>
+        <v>-9.756117025808067</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.52562410709454</v>
       </c>
       <c r="E91">
-        <v>-34.95832998066053</v>
+        <v>-28.924031646351</v>
       </c>
       <c r="F91">
-        <v>-4.958515471623637</v>
+        <v>-3.75028859912678</v>
       </c>
       <c r="G91">
-        <v>-13.94349158086696</v>
+        <v>-9.373209559607846</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.36802098071938</v>
       </c>
       <c r="E92">
-        <v>-36.119528411575</v>
+        <v>-30.65341222916431</v>
       </c>
       <c r="F92">
-        <v>-4.966076809276392</v>
+        <v>-3.677386469108603</v>
       </c>
       <c r="G92">
-        <v>-12.91655911206944</v>
+        <v>-10.00537133878313</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.27061427895508</v>
       </c>
       <c r="E93">
-        <v>-36.9163697661736</v>
+        <v>-32.29880241935561</v>
       </c>
       <c r="F93">
-        <v>-5.166115939908833</v>
+        <v>-3.812926428656867</v>
       </c>
       <c r="G93">
-        <v>-13.78293862074727</v>
+        <v>-9.826347360681309</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.23817317894686</v>
       </c>
       <c r="E94">
-        <v>-37.44115916615061</v>
+        <v>-33.35188445306215</v>
       </c>
       <c r="F94">
-        <v>-4.859002867157931</v>
+        <v>-3.937575841960525</v>
       </c>
       <c r="G94">
-        <v>-14.58155886430734</v>
+        <v>-9.964706381031949</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.27021895327488</v>
       </c>
       <c r="E95">
-        <v>-37.79972251266836</v>
+        <v>-34.60485847122702</v>
       </c>
       <c r="F95">
-        <v>-5.360343244843233</v>
+        <v>-4.393523342707221</v>
       </c>
       <c r="G95">
-        <v>-13.20729162973581</v>
+        <v>-9.762442859952333</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.35868164984356</v>
       </c>
       <c r="E96">
-        <v>-40.14379290779593</v>
+        <v>-36.11277736656649</v>
       </c>
       <c r="F96">
-        <v>-4.798377970416645</v>
+        <v>-4.337732798128674</v>
       </c>
       <c r="G96">
-        <v>-14.20576176100102</v>
+        <v>-10.62330064381996</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.49386178680881</v>
       </c>
       <c r="E97">
-        <v>-43.74693631191888</v>
+        <v>-38.86280547924509</v>
       </c>
       <c r="F97">
-        <v>-5.871751599942161</v>
+        <v>-4.423203746749527</v>
       </c>
       <c r="G97">
-        <v>-14.12904894730804</v>
+        <v>-10.30676483198732</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.65409360508533</v>
       </c>
       <c r="E98">
-        <v>-42.75018220680533</v>
+        <v>-40.86098397560696</v>
       </c>
       <c r="F98">
-        <v>-4.851041428049625</v>
+        <v>-4.750191838595798</v>
       </c>
       <c r="G98">
-        <v>-14.53483567373248</v>
+        <v>-10.82513208666975</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.82335881985851</v>
       </c>
       <c r="E99">
-        <v>-45.90292022577894</v>
+        <v>-42.62620261894221</v>
       </c>
       <c r="F99">
-        <v>-5.21518676811587</v>
+        <v>-4.778879030122148</v>
       </c>
       <c r="G99">
-        <v>-15.23060171800877</v>
+        <v>-10.91450309551274</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.97160774910793</v>
       </c>
       <c r="E100">
-        <v>-47.20756849924732</v>
+        <v>-44.07619044611731</v>
       </c>
       <c r="F100">
-        <v>-5.164459205103234</v>
+        <v>-5.130005748085997</v>
       </c>
       <c r="G100">
-        <v>-14.36577560236265</v>
+        <v>-12.43019305921258</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-19.0823054171532</v>
       </c>
       <c r="E101">
-        <v>-48.07514008101057</v>
+        <v>-45.46425493074205</v>
       </c>
       <c r="F101">
-        <v>-5.298641470478309</v>
+        <v>-5.386860113774248</v>
       </c>
       <c r="G101">
-        <v>-15.26320730720718</v>
+        <v>-12.01799173332777</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-19.12933857942185</v>
       </c>
       <c r="E102">
-        <v>-50.19266214309422</v>
+        <v>-47.76099117640054</v>
       </c>
       <c r="F102">
-        <v>-6.045506632883774</v>
+        <v>-5.369556347097169</v>
       </c>
       <c r="G102">
-        <v>-15.04211118001957</v>
+        <v>-11.8807292257054</v>
       </c>
     </row>
   </sheetData>
